--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1608-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1608-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42BF7272-B186-4C1A-ADD8-0492295ADE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D5D46F5-C7E7-4D6C-8D4B-172B4D2844D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{53847160-11BB-4A81-8C90-D55A8A62B3B6}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6559B0F2-548C-4777-B48F-8DD0962DDBB0}"/>
   </bookViews>
   <sheets>
     <sheet name="1608-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1580,29 +1580,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437DB8C5-A967-42BD-A90C-5A400DC99B88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDE645F-8358-4293-8B68-4D8C0E5E06EF}">
   <dimension ref="A1:X51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1636,7 +1635,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1672,7 +1671,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1724,7 +1723,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1792,7 +1791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2024</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>2023</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2022</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2021</v>
       </c>
@@ -2080,7 +2079,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2020</v>
       </c>
@@ -2152,7 +2151,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2019</v>
       </c>
@@ -2224,7 +2223,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>2018</v>
       </c>
@@ -2296,7 +2295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <v>2017</v>
       </c>
@@ -2368,7 +2367,7 @@
         <v>8.74</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2016</v>
       </c>
@@ -2440,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <v>2015</v>
       </c>
@@ -2512,7 +2511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2014</v>
       </c>
@@ -2584,7 +2583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2013</v>
       </c>
@@ -2656,7 +2655,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2012</v>
       </c>
@@ -2728,7 +2727,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="41">
         <v>2011</v>
       </c>
@@ -2800,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2010</v>
       </c>
@@ -2872,7 +2871,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="41">
         <v>2009</v>
       </c>
@@ -2944,7 +2943,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2008</v>
       </c>
@@ -3016,7 +3015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="41">
         <v>2007</v>
       </c>
@@ -3088,7 +3087,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2006</v>
       </c>
@@ -3160,7 +3159,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2005</v>
       </c>
@@ -3232,7 +3231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2004</v>
       </c>
@@ -3304,7 +3303,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2003</v>
       </c>
@@ -3376,7 +3375,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2002</v>
       </c>
@@ -3448,7 +3447,7 @@
         <v>9.91</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41">
         <v>2001</v>
       </c>
@@ -3520,7 +3519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2000</v>
       </c>
@@ -3592,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>1999</v>
       </c>
@@ -3664,7 +3663,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>1998</v>
       </c>
@@ -3736,7 +3735,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>1997</v>
       </c>
@@ -3808,7 +3807,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>1996</v>
       </c>
@@ -3880,7 +3879,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>1995</v>
       </c>
@@ -3952,7 +3951,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>1994</v>
       </c>
@@ -4024,7 +4023,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="43">
         <v>1993</v>
       </c>
@@ -4096,7 +4095,7 @@
         <v>7.91</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="45"/>
       <c r="B37" s="46"/>
       <c r="C37" s="20" t="s">
@@ -4124,7 +4123,7 @@
       <c r="W37" s="52"/>
       <c r="X37" s="48"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <v>1992</v>
       </c>
@@ -4196,7 +4195,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="55"/>
       <c r="B39" s="56"/>
       <c r="C39" s="22" t="s">
@@ -4224,7 +4223,7 @@
       <c r="W39" s="62"/>
       <c r="X39" s="58"/>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="43">
         <v>1991</v>
       </c>
@@ -4296,7 +4295,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="45"/>
       <c r="B41" s="46"/>
       <c r="C41" s="20" t="s">
@@ -4324,7 +4323,7 @@
       <c r="W41" s="52"/>
       <c r="X41" s="48"/>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <v>1990</v>
       </c>
@@ -4396,7 +4395,7 @@
         <v>8.42</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="55"/>
       <c r="B43" s="56"/>
       <c r="C43" s="22" t="s">
@@ -4424,7 +4423,7 @@
       <c r="W43" s="62"/>
       <c r="X43" s="58"/>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="41">
         <v>1989</v>
       </c>
@@ -4496,7 +4495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>1988</v>
       </c>
@@ -4568,7 +4567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="41">
         <v>1987</v>
       </c>
@@ -4640,7 +4639,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>1986</v>
       </c>
@@ -4712,7 +4711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
         <v>1985</v>
       </c>
@@ -4784,7 +4783,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>1984</v>
       </c>
@@ -4856,7 +4855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="41">
         <v>1983</v>
       </c>
@@ -4928,7 +4927,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39" t="s">
         <v>60</v>
       </c>
